--- a/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, maman emmène Ava à l'école. Sur le chemin, maman dit : à l'école, tu laves tes mains aussi. Comme à la maison. Ava range son manteau. Plus tard, Ava va aux toilettes. Après les toilettes, elle va ouvrir l'eau. Elle ouvre l'eau. Elle prend le savon. Elle frotte le dos des mains. Elle frotte entre les doigts. Elle rince. Elle essuie. La cloche sonne. C'est l'heure de manger. Avant de manger, Ava va au lavabo de la classe. Elle ouvre l'eau. Elle prend le savon. Elle rince. Elle essuie. La maîtresse sourit. Ava dit : comme avec maman, à la maison. Eau et savon, deux fois. Les mains sont propres. Ava s'assoit à table.</t>
+          <t>Le matin, maman emmène Ava à l'école. Sur le chemin, À l'école, tu laves tes mains aussi. Comme à la maison. Ava range son manteau. Plus tard, Ava va aux toilettes. Après les toilettes, elle va ouvrir l'eau. Elle ouvre l'eau. Elle prend le savon. Elle frotte le dos des mains. Elle frotte entre les doigts. Elle rince. Elle essuie. La cloche sonne. C'est l'heure de manger. Avant de manger, Ava va au lavabo de la classe. Elle ouvre l'eau. Elle prend le savon. Elle rince. Elle essuie. La maîtresse sourit. Comme avec maman, à la maison. Eau et savon, deux fois. Les mains sont propres. Ava s'assoit à table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, maman emmène Ava à l'école. Sur le chemin,
+maman|À l'école, tu laves tes mains aussi. Comme à la maison.
+narrateur|Ava range son manteau. Plus tard, Ava va aux toilettes. Après les toilettes, elle va ouvrir l'eau. Elle ouvre l'eau. Elle prend le savon. Elle frotte le dos des mains. Elle frotte entre les doigts. Elle rince. Elle essuie. La cloche sonne. C'est l'heure de manger. Avant de manger, Ava va au lavabo de la classe. Elle ouvre l'eau. Elle prend le savon. Elle rince. Elle essuie. La maîtresse sourit.
+enfant-f|Comme avec maman, à la maison. Eau et savon, deux fois.
+narrateur|Les mains sont propres. Ava s'assoit à table.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ava se lave les mains à l'école. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Après les toilettes, Ava a lavé. Avant de manger, Ava a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ava mange son goûter. Le soir, elle raconte à maman. Maman dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Les mains sont propres. Ava s'assoit à table.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Ava se lave les mains à l'école. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Après les toilettes, Ava a lavé. Avant de manger, Ava a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Ava mange son goûter. Le soir, elle raconte à maman. Maman dit merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ava se lave les mains à l'école</t>
+          <t>Comme à la maison</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le gravier craque. Maman dit : à l'école aussi. Après les toilettes, savon. Avant de manger, savon. Le soir, il raconte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, maman emmène Ava à l'école. Sur le chemin, À l'école, tu laves tes mains aussi. Comme à la maison. Ava range son manteau. Plus tard, Ava va aux toilettes. Après les toilettes, elle va ouvrir l'eau. Elle ouvre l'eau. Elle prend le savon. Elle frotte le dos des mains. Elle frotte entre les doigts. Elle rince. Elle essuie. La cloche sonne. C'est l'heure de manger. Avant de manger, Ava va au lavabo de la classe. Elle ouvre l'eau. Elle prend le savon. Elle rince. Elle essuie. La maîtresse sourit. Comme avec maman, à la maison. Eau et savon, deux fois. Les mains sont propres. Ava s'assoit à table.</t>
+          <t>Le gravier de la cour craque sous les chaussures. Une flaque brille près du portail. Le manteau de Victorino sent le vent. Un crochet attend déjà, dans le couloir. La vitre de la classe a une petite buée. Un savon vert attend près du lavabo. Il sent déjà la pomme, un peu. Victorino, tu laves tes mains à l'école aussi. Comme à la maison. Savon et eau. Oui. Savon et eau. En ce moment, Victorino range son manteau. Le crochet est un peu froid. Tu ranges le manteau ? Oui, maman. Bravo. Maman part, tout doucement. Plus tard, il va aux toilettes. Après les toilettes, il va au lavabo. Il ouvre l'eau. L'eau est tiède, comme à la maison. Il prend le savon. Le savon sent la pomme. Il frotte le dos des mains. Il frotte entre les doigts. Il rince. Il essuie. Comme avec maman. La cloche sonne. C'est l'heure de manger. Avant de manger, Victorino va au lavabo. Le lavabo de la classe est blanc. Il ouvre l'eau. Il prend le savon. Il rince. Il essuie. Eau et savon, deux fois. Les mains sont propres. Victorino s'assoit à table. Le goûter sent la pomme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le matin, maman emmène Ava à l'école. Sur le chemin,
-maman|À l'école, tu laves tes mains aussi. Comme à la maison.
-narrateur|Ava range son manteau. Plus tard, Ava va aux toilettes. Après les toilettes, elle va ouvrir l'eau. Elle ouvre l'eau. Elle prend le savon. Elle frotte le dos des mains. Elle frotte entre les doigts. Elle rince. Elle essuie. La cloche sonne. C'est l'heure de manger. Avant de manger, Ava va au lavabo de la classe. Elle ouvre l'eau. Elle prend le savon. Elle rince. Elle essuie. La maîtresse sourit.
-enfant-f|Comme avec maman, à la maison. Eau et savon, deux fois.
-narrateur|Les mains sont propres. Ava s'assoit à table.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le gravier de la cour craque sous les chaussures.
+narrateur|Une flaque brille près du portail.
+narrateur|Le manteau de Victorino sent le vent.
+narrateur|Un crochet attend déjà, dans le couloir.
+narrateur|La vitre de la classe a une petite buée.
+narrateur|Un savon vert attend près du lavabo.
+narrateur|Il sent déjà la pomme, un peu.
+maman|Victorino, tu laves tes mains à l'école aussi.
+maman|Comme à la maison.
+enfant-m|Savon et eau.
+maman|Oui.
+maman|Savon et eau.
+narrateur|En ce moment, Victorino range son manteau.
+narrateur|Le crochet est un peu froid.
+maman|Tu ranges le manteau ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Maman part, tout doucement.
+narrateur|Plus tard, il va aux toilettes.
+narrateur|Après les toilettes, il va au lavabo.
+narrateur|Il ouvre l'eau.
+narrateur|L'eau est tiède, comme à la maison.
+narrateur|Il prend le savon.
+narrateur|Le savon sent la pomme.
+narrateur|Il frotte le dos des mains.
+narrateur|Il frotte entre les doigts.
+narrateur|Il rince.
+narrateur|Il essuie.
+enfant-m|Comme avec maman.
+narrateur|La cloche sonne.
+narrateur|C'est l'heure de manger.
+narrateur|Avant de manger, Victorino va au lavabo.
+narrateur|Le lavabo de la classe est blanc.
+narrateur|Il ouvre l'eau.
+narrateur|Il prend le savon.
+narrateur|Il rince.
+narrateur|Il essuie.
+enfant-m|Eau et savon, deux fois.
+narrateur|Les mains sont propres.
+narrateur|Victorino s'assoit à table.
+narrateur|Le goûter sent la pomme.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cloche_ecole</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ava se lave les mains à l'école. Avec quoi ?</t>
+          <t>Victorino se lave les mains à l'école. Avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1556,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ava se lave les mains à l'école. Avec quoi ?</t>
+          <t>narrateur|Victorino se lave les mains à l'école.
+narrateur|Avec quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Après les toilettes, Ava a lavé. Avant de manger, Ava a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
+          <t>Après les toilettes, Victorino a lavé. Avant de manger, Victorino a lavé. Ouvrir l'eau, savon, rincer, essuyer. Le soir, maman l'écoute. Tu as pris le savon, à l'école ? Oui, maman. Le savon. Comme à la maison. Bravo. Tu as fait du bon travail. Victorino sent encore un peu la pomme.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1729,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Après les toilettes, Ava a lavé. Avant de manger, Ava a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
+          <t>narrateur|Après les toilettes, Victorino a lavé.
+narrateur|Avant de manger, Victorino a lavé.
+narrateur|Ouvrir l'eau, savon, rincer, essuyer.
+narrateur|Le soir, maman l'écoute.
+maman|Tu as pris le savon, à l'école ?
+enfant-m|Oui, maman.
+enfant-m|Le savon.
+maman|Comme à la maison.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Victorino sent encore un peu la pomme.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1767,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ava mange son goûter. Le soir, elle raconte à maman. Maman dit merci.</t>
+          <t>Victorino mange son goûter. La pomme croque un peu. Le soir, il raconte à maman. La lampe de la cuisine est allumée. Après les toilettes, savon. Avant de manger, savon. Deux fois, comme à la maison ? Oui. Deux fois. Tu as fini de raconter ? Oui, maman. Bravo, Victorino. Merci. Merci, maman. Le manteau sèche près de la porte. La maison sent le pain du soir. Une miette reste sur la table. Tu as les mains propres ? Oui, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1903,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ava mange son goûter. Le soir, elle raconte à maman. Maman dit merci.</t>
+          <t>narrateur|Victorino mange son goûter.
+narrateur|La pomme croque un peu.
+narrateur|Le soir, il raconte à maman.
+narrateur|La lampe de la cuisine est allumée.
+enfant-m|Après les toilettes, savon.
+enfant-m|Avant de manger, savon.
+maman|Deux fois, comme à la maison ?
+enfant-m|Oui.
+enfant-m|Deux fois.
+maman|Tu as fini de raconter ?
+enfant-m|Oui, maman.
+maman|Bravo, Victorino.
+maman|Merci.
+enfant-m|Merci, maman.
+narrateur|Le manteau sèche près de la porte.
+narrateur|La maison sent le pain du soir.
+narrateur|Une miette reste sur la table.
+maman|Tu as les mains propres ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1949,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les mains de Victorino sont propres. Savon et eau. Oui. Comme à la maison. Bravo, Victorino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2089,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Les mains de Victorino sont propres.
+enfant-m|Savon et eau.
+maman|Oui.
+maman|Comme à la maison.
+maman|Bravo, Victorino.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le matin, maman emmène Ava à l'école. Sur le chemin, maman dit : à l'école, tu laves tes mains aussi. Comme à la maison. Ava range son manteau. Plus tard, Ava va aux toilettes. Après les toilettes, elle va ouvrir l'eau. Elle ouvre l'eau. Elle prend le &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt;. Elle frotte le dos des mains. Elle frotte entre les doigts. Elle rince. Elle essuie. La cloche sonne. C'est l'heure de manger. Avant de manger, Ava va au lavabo de la classe. Elle ouvre l'eau. Elle prend le savon. Elle rince. Elle essuie. La maîtresse sourit. Ava dit : comme avec maman, à la maison. Eau et savon, deux fois. Les mains sont propres. Ava s'assoit à table.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le gravier de la cour craque sous les chaussures. Une flaque brille près du portail. Le manteau de Victorino sent le vent. Un crochet attend déjà, dans le couloir. La vitre de la classe a une petite buée. Un savon vert attend près du lavabo. Il sent déjà la pomme, un peu. Victorino, tu laves tes mains à l'école aussi. Comme à la maison. Savon et eau. Oui. Savon et eau. En ce moment, Victorino range son manteau. Le crochet est un peu froid. Tu ranges le manteau ? Oui, maman. Bravo. Maman part, tout doucement. Plus tard, il va aux toilettes. Après les toilettes, il va au lavabo. Il ouvre l'eau. L'eau est tiède, comme à la maison. Il prend le savon. Le savon sent la pomme. Il frotte le dos des mains. Il frotte entre les doigts. Il rince. Il essuie. Comme avec maman. La cloche sonne. C'est l'heure de manger. Avant de manger, Victorino va au lavabo. Le lavabo de la classe est blanc. Il ouvre l'eau. Il prend le savon. Il rince. Il essuie. Eau et savon, deux fois. Les mains sont propres. Victorino s'assoit à table. Le goûter sent la pomme.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ava se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s à l'école. Avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino se lave les mains à l'école. Avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1560,7 +1560,6 @@
 narrateur|Avec quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1585,12 +1584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Après les toilettes, Victorino a lavé. Avant de manger, Victorino a lavé. Ouvrir l'eau, savon, rincer, essuyer. Le soir, maman l'écoute. Tu as pris le savon, à l'école ? Oui, maman. Le savon. Comme à la maison. Bravo. Tu as fait du bon travail. Victorino sent encore un peu la pomme.</t>
+          <t>Après les toilettes, Victorino a lavé. Avant de manger, Victorino a lavé. Ouvrir l'eau, savon, rincer, essuyer. Le soir, maman l'écoute. Tu as pris le savon, à l'école ? Oui, maman. Le savon. Comme à la maison. Bravo. Victorino sent encore un peu la pomme.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après les toilettes, Ava a lavé. Avant de manger, Ava a lavé. Ouvrir l'eau, &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt;, rincer, essuyer.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après les toilettes, Victorino a lavé. Avant de manger, Victorino a lavé. Ouvrir l'eau, savon, rincer, essuyer. Le soir, maman l'écoute. Tu as pris le savon, à l'école ? Oui, maman. Le savon. Comme à la maison. Bravo. Victorino sent encore un peu la pomme.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1738,11 +1737,9 @@
 enfant-m|Le savon.
 maman|Comme à la maison.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Victorino sent encore un peu la pomme.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1772,7 +1769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ava mange son goûter. Le soir, elle raconte à maman. Maman dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino mange son goûter. La pomme croque un peu. Le soir, il raconte à maman. La lampe de la cuisine est allumée. Après les toilettes, savon. Avant de manger, savon. Deux fois, comme à la maison ? Oui. Deux fois. Tu as fini de raconter ? Oui, maman. Bravo, Victorino. Merci. Merci, maman. Le manteau sèche près de la porte. La maison sent le pain du soir. Une miette reste sur la table. Tu as les mains propres ? Oui, maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1924,7 +1921,6 @@
 enfant-m|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les mains de Victorino sont propres. Savon et eau. Oui. Comme à la maison. Bravo, Victorino. L'histoire est finie.</t>
+          <t>Les mains de Victorino sont propres. Savon et eau. Oui. Comme à la maison. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les mains de Victorino sont propres. Savon et eau. Oui. Comme à la maison. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2093,11 +2089,9 @@
 enfant-m|Savon et eau.
 maman|Oui.
 maman|Comme à la maison.
-maman|Bravo, Victorino.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Victorino.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2116,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2155,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école</t>
+          <t>chemin, école, lavabo de la classe</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ava, maman</t>
+          <t>Victorino, maman</t>
         </is>
       </c>
     </row>
